--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125124021</v>
+        <v>125124019</v>
       </c>
       <c r="B3" t="n">
-        <v>90397</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729795</v>
+        <v>729836</v>
       </c>
       <c r="R3" t="n">
-        <v>7086204</v>
+        <v>7086230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125124019</v>
+        <v>125124021</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>90397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729836</v>
+        <v>729795</v>
       </c>
       <c r="R4" t="n">
-        <v>7086230</v>
+        <v>7086204</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123971</v>
+        <v>125124019</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729866</v>
+        <v>729836</v>
       </c>
       <c r="R2" t="n">
-        <v>7086198</v>
+        <v>7086230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125124019</v>
+        <v>125124021</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729836</v>
+        <v>729795</v>
       </c>
       <c r="R3" t="n">
-        <v>7086230</v>
+        <v>7086204</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125124021</v>
+        <v>125123971</v>
       </c>
       <c r="B4" t="n">
-        <v>90397</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729795</v>
+        <v>729866</v>
       </c>
       <c r="R4" t="n">
-        <v>7086204</v>
+        <v>7086198</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125124019</v>
+        <v>125124021</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>90397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729836</v>
+        <v>729795</v>
       </c>
       <c r="R2" t="n">
-        <v>7086230</v>
+        <v>7086204</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125124021</v>
+        <v>125123971</v>
       </c>
       <c r="B3" t="n">
-        <v>90397</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729795</v>
+        <v>729866</v>
       </c>
       <c r="R3" t="n">
-        <v>7086204</v>
+        <v>7086198</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123971</v>
+        <v>125124019</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729866</v>
+        <v>729836</v>
       </c>
       <c r="R4" t="n">
-        <v>7086198</v>
+        <v>7086230</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123971</v>
+        <v>125124019</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729866</v>
+        <v>729836</v>
       </c>
       <c r="R3" t="n">
-        <v>7086198</v>
+        <v>7086230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125124019</v>
+        <v>125123971</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729836</v>
+        <v>729866</v>
       </c>
       <c r="R4" t="n">
-        <v>7086230</v>
+        <v>7086198</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125124019</v>
+        <v>125123971</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729836</v>
+        <v>729866</v>
       </c>
       <c r="R3" t="n">
-        <v>7086230</v>
+        <v>7086198</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123971</v>
+        <v>125124019</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729866</v>
+        <v>729836</v>
       </c>
       <c r="R4" t="n">
-        <v>7086198</v>
+        <v>7086230</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125124021</v>
       </c>
       <c r="B2" t="n">
-        <v>90397</v>
+        <v>90550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125123971</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125124019</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125124021</v>
+        <v>125124019</v>
       </c>
       <c r="B2" t="n">
-        <v>90550</v>
+        <v>91131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729795</v>
+        <v>729836</v>
       </c>
       <c r="R2" t="n">
-        <v>7086204</v>
+        <v>7086230</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123971</v>
+        <v>125124021</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>90550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729866</v>
+        <v>729795</v>
       </c>
       <c r="R3" t="n">
-        <v>7086198</v>
+        <v>7086204</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125124019</v>
+        <v>125123971</v>
       </c>
       <c r="B4" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729836</v>
+        <v>729866</v>
       </c>
       <c r="R4" t="n">
-        <v>7086230</v>
+        <v>7086198</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125124019</v>
+        <v>125124021</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729836</v>
+        <v>729795</v>
       </c>
       <c r="R2" t="n">
-        <v>7086230</v>
+        <v>7086204</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125124021</v>
+        <v>125124019</v>
       </c>
       <c r="B3" t="n">
-        <v>90550</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729795</v>
+        <v>729836</v>
       </c>
       <c r="R3" t="n">
-        <v>7086204</v>
+        <v>7086230</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,12 +872,7 @@
         <v>125123971</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,6 +963,111 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125773663</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Josjöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>729887</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7086232</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>125773663</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 19776-2025 artfynd.xlsx
+++ b/artfynd/A 19776-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>125773663</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
